--- a/Testing/Feedback/iMicroSeq_Field-Level-Feedback_v1.2.xlsx
+++ b/Testing/Feedback/iMicroSeq_Field-Level-Feedback_v1.2.xlsx
@@ -640,7 +640,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Return this workbook with your completed feedback form.</t>
+          <t>This workbook is optional. If you complete it, email it to Emma Griffiths (emma_griffiths@sfu.ca). The online feedback form is submitted separately and is the only required return.</t>
         </is>
       </c>
     </row>
